--- a/products.xlsx
+++ b/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,16 +442,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>P220</v>
+        <v>P222</v>
       </c>
       <c r="B2" t="str">
-        <v>Crinkled Silk Tiered Festive Dress</v>
+        <v>Azure Striped Organza Kaftan Set</v>
       </c>
       <c r="C2" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D2">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -460,22 +460,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G2" t="str">
-        <v>20_1788722727417-5687.jpeg</v>
+        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
       </c>
       <c r="H2" t="str">
-        <v>20_1788722727417-5687.jpeg</v>
+        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
       </c>
       <c r="I2" t="str">
-        <v>20_1788722727417-5687.jpeg</v>
+        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>In Stock</v>
       </c>
       <c r="K2" t="str">
-        <v>Festive Edit</v>
+        <v>Fresh Arrivals</v>
       </c>
       <c r="L2" t="str">
-        <v>This exquisite fusion dress features alternating tiers of olive green and vibrant fuchsia in a beautifully crinkled silk fabric that drapes effortlessly. Accentuated with a delicate gold zari border at the waist and hem, this sleeveless silhouette seamlessly blends traditional elegance with contemporary style, making it perfect for festive gatherings and intimate celebrations. Note: No Return Policy.</v>
+        <v>Exude ethereal grace in this breezy azure kaftan, meticulously crafted from lightweight organza and adorned with delicate metallic stripes. The neckline features intricate hand-embellished detailing, making it a perfect choice for sophisticated daytime soirées or intimate festive gatherings. Note: No Return Policy.</v>
       </c>
       <c r="M2" t="str">
         <v>Yes</v>
@@ -483,16 +483,16 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>P219</v>
+        <v>P221</v>
       </c>
       <c r="B3" t="str">
-        <v>Blush Pink Floral Embroidered Dress</v>
+        <v>Classic Plaid Collared</v>
       </c>
       <c r="C3" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D3">
-        <v>3500</v>
+        <v>5000</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -501,13 +501,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G3" t="str">
-        <v>19_1788722006967-4942.jpeg</v>
+        <v>8f5a4626-3db0-4e69-a246-419e546a855b_1789557487096-4376.jpg</v>
       </c>
       <c r="H3" t="str">
-        <v>19_1788722006967-4942.jpeg</v>
+        <v>716e7a91-0f8a-49de-8690-24045d24f11c_1789557513967-1019.jpg</v>
       </c>
       <c r="I3" t="str">
-        <v>19_1788722006967-4942.jpeg</v>
+        <v>8f5a4626-3db0-4e69-a246-419e546a855b_1789557487096-4376.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>In Stock</v>
@@ -516,7 +516,7 @@
         <v>Fresh Arrivals</v>
       </c>
       <c r="L3" t="str">
-        <v>Crafted from lightweight, flowing georgette in a dreamy blush pink hue, this ankle-length dress features a flattering square neckline and elegant three-quarter puff sleeves. Delicate hand-embroidered floral borders adorn the bodice, complemented by matching floral motifs along the ruffled hemline for a touch of whimsical charm. Perfect for intimate festive gatherings, daytime celebrations, or elegant soirées, this piece effortlessly blends modern grace with traditional craftsmanship. Note: No Return Policy.</v>
+        <v>Exuding understated elegance, this refined midi dress features a timeless plaid pattern tailored in breathable, high-quality cotton. Its sophisticated notch-collar silhouette and graceful flare make it a versatile choice for intimate festive gatherings or elevated daytime events. Note: No Return Policy.</v>
       </c>
       <c r="M3" t="str">
         <v>Yes</v>
@@ -524,10 +524,10 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>P218</v>
+        <v>P220</v>
       </c>
       <c r="B4" t="str">
-        <v>Midnight Blue Woven Zari Lehenga</v>
+        <v>Crinkled Silk Tiered Festive Dress</v>
       </c>
       <c r="C4" t="str">
         <v>Ladies Wear</v>
@@ -542,22 +542,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G4" t="str">
-        <v>18_1788721975689-8954.jpeg</v>
+        <v>20_1788722727417-5687.jpeg</v>
       </c>
       <c r="H4" t="str">
-        <v>18_1788721975689-8954.jpeg</v>
+        <v>20_1788722727417-5687.jpeg</v>
       </c>
       <c r="I4" t="str">
-        <v>18_1788721975689-8954.jpeg</v>
+        <v>20_1788722727417-5687.jpeg</v>
       </c>
       <c r="J4" t="str">
         <v>In Stock</v>
       </c>
       <c r="K4" t="str">
-        <v>Handcrafted Couture</v>
+        <v>Festive Edit</v>
       </c>
       <c r="L4" t="str">
-        <v>Draped in a majestic midnight blue hue, this voluminous flared lehenga features subtle checkered weave accents paired with a rich metallic gold zari woven border at the hemline. Complemented by a tailored elbow-sleeve blouse and a lightweight sheer tulle dupatta trimmed with ornate brocade borders, it stands as a quintessential choice for grand receptions and festive soirées. Note: No Return Policy.</v>
+        <v>This exquisite fusion dress features alternating tiers of olive green and vibrant fuchsia in a beautifully crinkled silk fabric that drapes effortlessly. Accentuated with a delicate gold zari border at the waist and hem, this sleeveless silhouette seamlessly blends traditional elegance with contemporary style, making it perfect for festive gatherings and intimate celebrations. Note: No Return Policy.</v>
       </c>
       <c r="M4" t="str">
         <v>Yes</v>
@@ -565,16 +565,16 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>P217</v>
+        <v>P219</v>
       </c>
       <c r="B5" t="str">
-        <v>Emerald Ivory Tissue Lehenga Set</v>
+        <v>Blush Pink Floral Embroidered Dress</v>
       </c>
       <c r="C5" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D5">
-        <v>8500</v>
+        <v>3500</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -583,22 +583,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G5" t="str">
-        <v>16_1788721959182-4092.jpeg</v>
+        <v>19_1788722006967-4942.jpeg</v>
       </c>
       <c r="H5" t="str">
-        <v>16_1788721959182-4092.jpeg</v>
+        <v>19_1788722006967-4942.jpeg</v>
       </c>
       <c r="I5" t="str">
-        <v>16_1788721959182-4092.jpeg</v>
+        <v>19_1788722006967-4942.jpeg</v>
       </c>
       <c r="J5" t="str">
         <v>In Stock</v>
       </c>
       <c r="K5" t="str">
-        <v>Festive Edit</v>
+        <v>Fresh Arrivals</v>
       </c>
       <c r="L5" t="str">
-        <v>Exuding timeless grace, this ensemble features a delicately woven off-white tissue skirt seamlessly paired with a rich emerald green blouse adorned with intricate gold motifs. The look is complete with a lightweight sheer dupatta trimmed in a regal zari lace border, perfect for intimate wedding ceremonies and festive celebrations. Note: No Return Policy.</v>
+        <v>Crafted from lightweight, flowing georgette in a dreamy blush pink hue, this ankle-length dress features a flattering square neckline and elegant three-quarter puff sleeves. Delicate hand-embroidered floral borders adorn the bodice, complemented by matching floral motifs along the ruffled hemline for a touch of whimsical charm. Perfect for intimate festive gatherings, daytime celebrations, or elegant soirées, this piece effortlessly blends modern grace with traditional craftsmanship. Note: No Return Policy.</v>
       </c>
       <c r="M5" t="str">
         <v>Yes</v>
@@ -606,16 +606,16 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>P216</v>
+        <v>P218</v>
       </c>
       <c r="B6" t="str">
-        <v>Teal Zari Kurta and Ivory Skirt</v>
+        <v>Midnight Blue Woven Zari Lehenga</v>
       </c>
       <c r="C6" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D6">
-        <v>6500</v>
+        <v>4500</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -624,22 +624,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G6" t="str">
-        <v>15_1788721934285-9936.jpeg</v>
+        <v>18_1788721975689-8954.jpeg</v>
       </c>
       <c r="H6" t="str">
-        <v>15_1788721934285-9936.jpeg</v>
+        <v>18_1788721975689-8954.jpeg</v>
       </c>
       <c r="I6" t="str">
-        <v>15_1788721934285-9936.jpeg</v>
+        <v>18_1788721975689-8954.jpeg</v>
       </c>
       <c r="J6" t="str">
         <v>In Stock</v>
       </c>
       <c r="K6" t="str">
-        <v>Festive Edit</v>
+        <v>Handcrafted Couture</v>
       </c>
       <c r="L6" t="str">
-        <v>This elegant ensemble features a sleeveless short kurta in deep peacock teal, adorned with delicate gold zari butis and finished with a rich crimson border, paired beautifully with a voluminous off-white flared skirt. Perfect for festive celebrations and intimate wedding gatherings, this contemporary take on traditional Kerala aesthetics exudes effortless grace and sophistication. Note: No Return Policy.</v>
+        <v>Draped in a majestic midnight blue hue, this voluminous flared lehenga features subtle checkered weave accents paired with a rich metallic gold zari woven border at the hemline. Complemented by a tailored elbow-sleeve blouse and a lightweight sheer tulle dupatta trimmed with ornate brocade borders, it stands as a quintessential choice for grand receptions and festive soirées. Note: No Return Policy.</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -647,16 +647,16 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>P215</v>
+        <v>P217</v>
       </c>
       <c r="B7" t="str">
-        <v>Royal Teal Flared Georgette Anarkali</v>
+        <v>Emerald Ivory Tissue Lehenga Set</v>
       </c>
       <c r="C7" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D7">
-        <v>3500</v>
+        <v>8500</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -665,13 +665,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G7" t="str">
-        <v>14_1788721913987-3936.jpeg</v>
+        <v>16_1788721959182-4092.jpeg</v>
       </c>
       <c r="H7" t="str">
-        <v>14_1788721913987-3936.jpeg</v>
+        <v>16_1788721959182-4092.jpeg</v>
       </c>
       <c r="I7" t="str">
-        <v>14_1788721913987-3936.jpeg</v>
+        <v>16_1788721959182-4092.jpeg</v>
       </c>
       <c r="J7" t="str">
         <v>In Stock</v>
@@ -680,7 +680,7 @@
         <v>Festive Edit</v>
       </c>
       <c r="L7" t="str">
-        <v>Draped in rich peacock teal georgette, this floor-length Anarkali ensemble exudes timeless elegance with its sweeping flared silhouette and fitted full sleeves. The look is beautifully complemented by a lightweight sheer dupatta adorned with delicate embroidered silver lace borders, making it an exquisite choice for regal celebrations and evening festivities. Note: No Return Policy.</v>
+        <v>Exuding timeless grace, this ensemble features a delicately woven off-white tissue skirt seamlessly paired with a rich emerald green blouse adorned with intricate gold motifs. The look is complete with a lightweight sheer dupatta trimmed in a regal zari lace border, perfect for intimate wedding ceremonies and festive celebrations. Note: No Return Policy.</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -688,16 +688,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>P214</v>
+        <v>P216</v>
       </c>
       <c r="B8" t="str">
-        <v>Royal Blue Pearl Embellished Sharara Set</v>
+        <v>Teal Zari Kurta and Ivory Skirt</v>
       </c>
       <c r="C8" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D8">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -706,13 +706,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G8" t="str">
-        <v>13_1788721896896-5264.jpeg</v>
+        <v>15_1788721934285-9936.jpeg</v>
       </c>
       <c r="H8" t="str">
-        <v>13_1788721896896-5264.jpeg</v>
+        <v>15_1788721934285-9936.jpeg</v>
       </c>
       <c r="I8" t="str">
-        <v>13_1788721896896-5264.jpeg</v>
+        <v>15_1788721934285-9936.jpeg</v>
       </c>
       <c r="J8" t="str">
         <v>In Stock</v>
@@ -721,7 +721,7 @@
         <v>Festive Edit</v>
       </c>
       <c r="L8" t="str">
-        <v>Rendered in an opulent royal blue georgette fabric, this breathtaking ensemble features a short tunic delicately detailed with pearl work along the square neckline and scalloped hemline. Paired with a gracefully voluminous flared bottom and a translucent dupatta bordered in pearls, it creates a silhouette of captivating elegance. Ideal for festive soirees, sangeet celebrations, and grand evening receptions. Note: No Return Policy.</v>
+        <v>This elegant ensemble features a sleeveless short kurta in deep peacock teal, adorned with delicate gold zari butis and finished with a rich crimson border, paired beautifully with a voluminous off-white flared skirt. Perfect for festive celebrations and intimate wedding gatherings, this contemporary take on traditional Kerala aesthetics exudes effortless grace and sophistication. Note: No Return Policy.</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -729,16 +729,16 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>P213</v>
+        <v>P215</v>
       </c>
       <c r="B9" t="str">
-        <v>Teal Wave Print Jacket Ensemble</v>
+        <v>Royal Teal Flared Georgette Anarkali</v>
       </c>
       <c r="C9" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D9">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -747,22 +747,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G9" t="str">
-        <v>12_1788721878497-6401.jpeg</v>
+        <v>14_1788721913987-3936.jpeg</v>
       </c>
       <c r="H9" t="str">
-        <v>12_1788721878497-6401.jpeg</v>
+        <v>14_1788721913987-3936.jpeg</v>
       </c>
       <c r="I9" t="str">
-        <v>12_1788721878497-6401.jpeg</v>
+        <v>14_1788721913987-3936.jpeg</v>
       </c>
       <c r="J9" t="str">
         <v>In Stock</v>
       </c>
       <c r="K9" t="str">
-        <v>Fresh Arrivals</v>
+        <v>Festive Edit</v>
       </c>
       <c r="L9" t="str">
-        <v>Exquisitely tailored in vibrant ocean-teal tones, this modern two-piece ensemble features a sleek inner dress layered under a mandarin-collared jacket adorned with rhythmic chevron wave patterns. Designed with seamless side pockets and effortless drape, it is an ideal choice for boutique gatherings, festive lunches, and contemporary soirées. Note: No Return Policy.</v>
+        <v>Draped in rich peacock teal georgette, this floor-length Anarkali ensemble exudes timeless elegance with its sweeping flared silhouette and fitted full sleeves. The look is beautifully complemented by a lightweight sheer dupatta adorned with delicate embroidered silver lace borders, making it an exquisite choice for regal celebrations and evening festivities. Note: No Return Policy.</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
@@ -770,16 +770,16 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>P212</v>
+        <v>P214</v>
       </c>
       <c r="B10" t="str">
-        <v>Midnight Blue Shimmer Anarkali Gown</v>
+        <v>Royal Blue Pearl Embellished Sharara Set</v>
       </c>
       <c r="C10" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D10">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -788,13 +788,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G10" t="str">
-        <v>11_1788721855287-4057.jpeg</v>
+        <v>13_1788721896896-5264.jpeg</v>
       </c>
       <c r="H10" t="str">
-        <v>11_1788721855287-4057.jpeg</v>
+        <v>13_1788721896896-5264.jpeg</v>
       </c>
       <c r="I10" t="str">
-        <v>11_1788721855287-4057.jpeg</v>
+        <v>13_1788721896896-5264.jpeg</v>
       </c>
       <c r="J10" t="str">
         <v>In Stock</v>
@@ -803,7 +803,7 @@
         <v>Festive Edit</v>
       </c>
       <c r="L10" t="str">
-        <v>Crafted in deep navy georgette woven with luminous metallic zari pinstripes, this sleeveless Anarkali gown embodies effortless modern grace. The structured V-neckline is highlighted with delicate hand-stitched detailing, cascading gracefully into a voluminous, fluid silhouette ideal for evening celebrations and festive gatherings. Note: No Return Policy.</v>
+        <v>Rendered in an opulent royal blue georgette fabric, this breathtaking ensemble features a short tunic delicately detailed with pearl work along the square neckline and scalloped hemline. Paired with a gracefully voluminous flared bottom and a translucent dupatta bordered in pearls, it creates a silhouette of captivating elegance. Ideal for festive soirees, sangeet celebrations, and grand evening receptions. Note: No Return Policy.</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -811,16 +811,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>P211</v>
+        <v>P213</v>
       </c>
       <c r="B11" t="str">
-        <v>Crimson Gold Embellished Bridal Lehenga</v>
+        <v>Teal Wave Print Jacket Ensemble</v>
       </c>
       <c r="C11" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D11">
-        <v>25000</v>
+        <v>4500</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -829,22 +829,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G11" t="str">
-        <v>10_1788721631854-5301.png</v>
+        <v>12_1788721878497-6401.jpeg</v>
       </c>
       <c r="H11" t="str">
-        <v>10_1788721631854-5301.png</v>
+        <v>12_1788721878497-6401.jpeg</v>
       </c>
       <c r="I11" t="str">
-        <v>10_1788721631854-5301.png</v>
+        <v>12_1788721878497-6401.jpeg</v>
       </c>
       <c r="J11" t="str">
         <v>In Stock</v>
       </c>
       <c r="K11" t="str">
-        <v>Bridal Heritage</v>
+        <v>Fresh Arrivals</v>
       </c>
       <c r="L11" t="str">
-        <v>Exuding regal splendor, this opulent bridal ensemble features a richly detailed crimson blouse adorned with intricate zardozi hand embroidery and sheer embellished sleeves, paired with a shimmering woven gold lehenga skirt. Completed with a luxurious tissue dupatta, it is meticulously tailored for grand wedding receptions and evening celebrations. Note: No Return Policy.</v>
+        <v>Exquisitely tailored in vibrant ocean-teal tones, this modern two-piece ensemble features a sleek inner dress layered under a mandarin-collared jacket adorned with rhythmic chevron wave patterns. Designed with seamless side pockets and effortless drape, it is an ideal choice for boutique gatherings, festive lunches, and contemporary soirées. Note: No Return Policy.</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -852,16 +852,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>P210</v>
+        <v>P212</v>
       </c>
       <c r="B12" t="str">
-        <v>Royal Blue Brocade Halter Blouse</v>
+        <v>Midnight Blue Shimmer Anarkali Gown</v>
       </c>
       <c r="C12" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D12">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -870,13 +870,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G12" t="str">
-        <v>9_1788721582211-8463.png</v>
+        <v>11_1788721855287-4057.jpeg</v>
       </c>
       <c r="H12" t="str">
-        <v>9_1788721582211-8463.png</v>
+        <v>11_1788721855287-4057.jpeg</v>
       </c>
       <c r="I12" t="str">
-        <v>9_1788721582211-8463.png</v>
+        <v>11_1788721855287-4057.jpeg</v>
       </c>
       <c r="J12" t="str">
         <v>In Stock</v>
@@ -885,294 +885,292 @@
         <v>Festive Edit</v>
       </c>
       <c r="L12" t="str">
+        <v>Crafted in deep navy georgette woven with luminous metallic zari pinstripes, this sleeveless Anarkali gown embodies effortless modern grace. The structured V-neckline is highlighted with delicate hand-stitched detailing, cascading gracefully into a voluminous, fluid silhouette ideal for evening celebrations and festive gatherings. Note: No Return Policy.</v>
+      </c>
+      <c r="M12" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>P211</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Crimson Gold Embellished Bridal Lehenga</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D13">
+        <v>25000</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G13" t="str">
+        <v>10_1788721631854-5301.png</v>
+      </c>
+      <c r="H13" t="str">
+        <v>10_1788721631854-5301.png</v>
+      </c>
+      <c r="I13" t="str">
+        <v>10_1788721631854-5301.png</v>
+      </c>
+      <c r="J13" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K13" t="str">
+        <v>Bridal Heritage</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Exuding regal splendor, this opulent bridal ensemble features a richly detailed crimson blouse adorned with intricate zardozi hand embroidery and sheer embellished sleeves, paired with a shimmering woven gold lehenga skirt. Completed with a luxurious tissue dupatta, it is meticulously tailored for grand wedding receptions and evening celebrations. Note: No Return Policy.</v>
+      </c>
+      <c r="M13" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>P210</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Royal Blue Brocade Halter Blouse</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D14">
+        <v>4500</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G14" t="str">
+        <v>9_1788721582211-8463.png</v>
+      </c>
+      <c r="H14" t="str">
+        <v>9_1788721582211-8463.png</v>
+      </c>
+      <c r="I14" t="str">
+        <v>9_1788721582211-8463.png</v>
+      </c>
+      <c r="J14" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K14" t="str">
+        <v>Festive Edit</v>
+      </c>
+      <c r="L14" t="str">
         <v>Impeccably tailored from lustrous royal blue silk brocade, this high-neck halter blouse features intricate woven gold zari floral motifs that radiate contemporary charm. Perfectly paired with ivory kasavu drapes or festive lehengas, it offers a striking silhouette ideal for evening celebrations and wedding receptions. Note: No Return Policy.</v>
       </c>
-      <c r="M12" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="13" xml:space="preserve">
-      <c r="A13" t="str">
+      <c r="M14" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
         <v>P209</v>
       </c>
-      <c r="B13" t="str">
+      <c r="B15" t="str">
         <v>Ivory Kasavu Striped Kurta Mundu Set</v>
       </c>
-      <c r="C13" t="str">
+      <c r="C15" t="str">
         <v>Mens Wear</v>
       </c>
-      <c r="D13">
+      <c r="D15">
         <v>3500</v>
       </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="str">
         <v>38 (S), 40 (M), 42 (L), 44 (XL)</v>
       </c>
-      <c r="G13" t="str">
+      <c r="G15" t="str">
         <v>8_1788721559495-2695.png</v>
       </c>
-      <c r="H13" t="str">
+      <c r="H15" t="str">
         <v>8_1788721559495-2695.png</v>
       </c>
-      <c r="I13" t="str">
+      <c r="I15" t="str">
         <v>8_1788721559495-2695.png</v>
       </c>
-      <c r="J13" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K13" t="str">
+      <c r="J15" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K15" t="str">
         <v>Festive Edit</v>
       </c>
-      <c r="L13" t="str" xml:space="preserve">
+      <c r="L15" t="str" xml:space="preserve">
         <v xml:space="preserve">Imbued with understated elegance, this pristine off-white kurta features delicate vertical gold kasavu zari stripes for a refined festive charm. Paired impeccably with a traditional golden zari-bordered mundu, this ensemble honors Kerala's rich sartorial heritage with contemporary elegance. Perfect for Onam celebrations, traditional wedding ceremonies, and auspicious festive rituals.
 Note: No Return Policy.</v>
       </c>
-      <c r="M13" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
-      <c r="A14" t="str">
+      <c r="M15" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16" xml:space="preserve">
+      <c r="A16" t="str">
         <v>P208</v>
       </c>
-      <c r="B14" t="str">
+      <c r="B16" t="str">
         <v>Ivory Floral Hand-Painted Kasavu Saree</v>
       </c>
-      <c r="C14" t="str">
-        <v>Ladies Wear</v>
-      </c>
-      <c r="D14">
+      <c r="C16" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D16">
         <v>5000</v>
       </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-      <c r="F14" t="str">
-        <v>S, M, L, XL</v>
-      </c>
-      <c r="G14" t="str">
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G16" t="str">
         <v>7_1788721516950-7398.png</v>
       </c>
-      <c r="H14" t="str">
+      <c r="H16" t="str">
         <v>7_1788721516950-7398.png</v>
       </c>
-      <c r="I14" t="str">
+      <c r="I16" t="str">
         <v>7_1788721516950-7398.png</v>
       </c>
-      <c r="J14" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K14" t="str">
+      <c r="J16" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K16" t="str">
         <v>Handcrafted Couture</v>
       </c>
-      <c r="L14" t="str" xml:space="preserve">
+      <c r="L16" t="str" xml:space="preserve">
         <v xml:space="preserve">This exquisite ivory Kasavu saree celebrates Kerala's rich heritage, beautifully adorned with delicate, hand-painted floral motifs in soft pink and leafy green hues. Crafted from premium handloom cotton, it features a classic golden zari border paired with a matching puff-sleeved blouse that exudes vintage grace. Perfect for Onam festivities, temple visits, or intimate wedding celebrations, this drape is a timeless ode to traditional elegance.
 Note: No Return Policy.</v>
       </c>
-      <c r="M14" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="15" xml:space="preserve">
-      <c r="A15" t="str">
+      <c r="M16" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
         <v>P207</v>
       </c>
-      <c r="B15" t="str">
+      <c r="B17" t="str">
         <v>Ivory Kasavu Embroidered Corset Gown</v>
       </c>
-      <c r="C15" t="str">
+      <c r="C17" t="str">
         <v>Customization</v>
       </c>
-      <c r="D15">
+      <c r="D17">
         <v>14000</v>
       </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-      <c r="F15" t="str">
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="str">
         <v>Custom Fit</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G17" t="str">
         <v>5_1788721479116-3197.png</v>
       </c>
-      <c r="H15" t="str">
+      <c r="H17" t="str">
         <v>5_1788721479116-3197.png</v>
       </c>
-      <c r="I15" t="str">
+      <c r="I17" t="str">
         <v>5_1788721479116-3197.png</v>
       </c>
-      <c r="J15" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K15" t="str">
+      <c r="J17" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K17" t="str">
         <v>Bespoke Couture</v>
       </c>
-      <c r="L15" t="str" xml:space="preserve">
+      <c r="L17" t="str" xml:space="preserve">
         <v xml:space="preserve">Reimagining traditional Kerala heritage with modern allure, this ivory gown features a structured strapless corset bodice delicately detailed with hand-embroidered golden motifs. Highlighted by classic golden Kasavu zari borders running down the fitted silhouette, it effortlessly blends regal grace with contemporary elegance. Perfectly suited for grand wedding receptions, engagement ceremonies, and opulent festive celebrations.
 Note: No Return Policy.</v>
       </c>
-      <c r="M15" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
+      <c r="M17" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18" xml:space="preserve">
+      <c r="A18" t="str">
         <v>P206</v>
       </c>
-      <c r="B16" t="str">
+      <c r="B18" t="str">
         <v>Scarlet Embroidered Organza Fusion Set</v>
       </c>
-      <c r="C16" t="str">
-        <v>Ladies Wear</v>
-      </c>
-      <c r="D16">
+      <c r="C18" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D18">
         <v>3550</v>
       </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="str">
-        <v>S, M, L, XL</v>
-      </c>
-      <c r="G16" t="str">
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G18" t="str">
         <v>6_1788721385434-2405.png</v>
       </c>
-      <c r="H16" t="str">
+      <c r="H18" t="str">
         <v>6_1788721385434-2405.png</v>
       </c>
-      <c r="I16" t="str">
+      <c r="I18" t="str">
         <v>6_1788721385434-2405.png</v>
       </c>
-      <c r="J16" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K16" t="str">
+      <c r="J18" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K18" t="str">
         <v>Festive Edit</v>
       </c>
-      <c r="L16" t="str" xml:space="preserve">
+      <c r="L18" t="str" xml:space="preserve">
         <v xml:space="preserve">Radiate contemporary elegance in this striking scarlet red fusion ensemble, featuring a tailored bustier paired with fluid trousers and a sheer organza longline jacket. The lightweight jacket is beautifully elevated by delicate scalloped gold zari embroidery tracing the borders and cuffs, adding a touch of traditional craftsmanship to a modern silhouette. Perfect for festive soirées, pre-wedding celebrations, or evening receptions, this ensemble effortlessly balances modern sophistication with timeless grace.
 Note: No Return Policy.</v>
       </c>
-      <c r="M16" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
-        <v>P201</v>
-      </c>
-      <c r="B17" t="str">
-        <v>Hand painted Kerala Kasavu saree</v>
-      </c>
-      <c r="C17" t="str">
-        <v>Ladies Wear</v>
-      </c>
-      <c r="D17">
-        <v>4200</v>
-      </c>
-      <c r="E17">
-        <v>4950</v>
-      </c>
-      <c r="F17" t="str">
-        <v>S, M, L, XL</v>
-      </c>
-      <c r="G17" t="str">
-        <v>7_1788628563833-9707.png</v>
-      </c>
-      <c r="H17" t="str">
-        <v>7_1788628563833-9707.png</v>
-      </c>
-      <c r="I17" t="str">
-        <v>7_1788628563833-9707.png</v>
-      </c>
-      <c r="J17" t="str">
-        <v>Made to Order</v>
-      </c>
-      <c r="K17" t="str">
-        <v>Fresh Arrivals</v>
-      </c>
-      <c r="L17" t="str" xml:space="preserve">
-        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
-Note: No Return Policy.</v>
-      </c>
-      <c r="M17" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
-        <v>P203</v>
-      </c>
-      <c r="B18" t="str">
-        <v>Purple gown</v>
-      </c>
-      <c r="C18" t="str">
-        <v>Customization</v>
-      </c>
-      <c r="D18">
-        <v>17500</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="str">
-        <v>Custom Fit</v>
-      </c>
-      <c r="G18" t="str">
-        <v>3_1788531630686-7753.jpeg</v>
-      </c>
-      <c r="H18" t="str">
-        <v>3_1788531630686-7753.jpeg</v>
-      </c>
-      <c r="I18" t="str">
-        <v>3_1788531630686-7753.jpeg</v>
-      </c>
-      <c r="J18" t="str">
-        <v>Limited Stock</v>
-      </c>
-      <c r="K18" t="str">
-        <v>Fresh Arrivals</v>
-      </c>
-      <c r="L18" t="str" xml:space="preserve">
-        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
-Note: No Return Policy.</v>
-      </c>
       <c r="M18" t="str">
         <v>Yes</v>
       </c>
     </row>
     <row r="19" xml:space="preserve">
       <c r="A19" t="str">
-        <v>P204</v>
+        <v>P201</v>
       </c>
       <c r="B19" t="str">
-        <v>Ivory top and pant</v>
+        <v>Hand painted Kerala Kasavu saree</v>
       </c>
       <c r="C19" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D19">
-        <v>6500</v>
+        <v>4200</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>4950</v>
       </c>
       <c r="F19" t="str">
         <v>S, M, L, XL</v>
       </c>
       <c r="G19" t="str">
-        <v>1_1788531606882-8672.jpeg</v>
+        <v>7_1788628563833-9707.png</v>
       </c>
       <c r="H19" t="str">
-        <v>1_1788531606882-8672.jpeg</v>
+        <v>7_1788628563833-9707.png</v>
       </c>
       <c r="I19" t="str">
-        <v>1_1788531606882-8672.jpeg</v>
+        <v>7_1788628563833-9707.png</v>
       </c>
       <c r="J19" t="str">
-        <v>In Stock</v>
+        <v>Made to Order</v>
       </c>
       <c r="K19" t="str">
         <v>Fresh Arrivals</v>
@@ -1187,16 +1185,16 @@
     </row>
     <row r="20" xml:space="preserve">
       <c r="A20" t="str">
-        <v>P205</v>
+        <v>P203</v>
       </c>
       <c r="B20" t="str">
-        <v>MODAL SLIK KAFTAN</v>
+        <v>Purple gown</v>
       </c>
       <c r="C20" t="str">
         <v>Customization</v>
       </c>
       <c r="D20">
-        <v>7500</v>
+        <v>17500</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1205,34 +1203,118 @@
         <v>Custom Fit</v>
       </c>
       <c r="G20" t="str">
-        <v>2_1788531469161-2419.jpeg</v>
+        <v>3_1788531630686-7753.jpeg</v>
       </c>
       <c r="H20" t="str">
-        <v>2_1788531469161-2419.jpeg</v>
+        <v>3_1788531630686-7753.jpeg</v>
       </c>
       <c r="I20" t="str">
-        <v>2_1788531469161-2419.jpeg</v>
+        <v>3_1788531630686-7753.jpeg</v>
       </c>
       <c r="J20" t="str">
-        <v>Made to Order</v>
+        <v>Limited Stock</v>
       </c>
       <c r="K20" t="str">
         <v>Fresh Arrivals</v>
       </c>
       <c r="L20" t="str" xml:space="preserve">
+        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
+Note: No Return Policy.</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="21" xml:space="preserve">
+      <c r="A21" t="str">
+        <v>P204</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Ivory top and pant</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D21">
+        <v>6500</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G21" t="str">
+        <v>1_1788531606882-8672.jpeg</v>
+      </c>
+      <c r="H21" t="str">
+        <v>1_1788531606882-8672.jpeg</v>
+      </c>
+      <c r="I21" t="str">
+        <v>1_1788531606882-8672.jpeg</v>
+      </c>
+      <c r="J21" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Fresh Arrivals</v>
+      </c>
+      <c r="L21" t="str" xml:space="preserve">
+        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
+Note: No Return Policy.</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>P205</v>
+      </c>
+      <c r="B22" t="str">
+        <v>MODAL SLIK KAFTAN</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="D22">
+        <v>7500</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <v>Custom Fit</v>
+      </c>
+      <c r="G22" t="str">
+        <v>2_1788531469161-2419.jpeg</v>
+      </c>
+      <c r="H22" t="str">
+        <v>2_1788531469161-2419.jpeg</v>
+      </c>
+      <c r="I22" t="str">
+        <v>2_1788531469161-2419.jpeg</v>
+      </c>
+      <c r="J22" t="str">
+        <v>Made to Order</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Fresh Arrivals</v>
+      </c>
+      <c r="L22" t="str" xml:space="preserve">
         <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
 Neck hand worked
 above excel price will vary 500-1000 rs
 customization possible
 Note: No Return Policy.</v>
       </c>
-      <c r="M20" t="str">
+      <c r="M22" t="str">
         <v>Yes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M20"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/products.xlsx
+++ b/products.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M28"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -442,81 +442,82 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>P222</v>
+        <v>P230</v>
       </c>
       <c r="B2" t="str">
-        <v>Azure Striped Organza Kaftan Set</v>
+        <v>Pistachio Floral Embroidered Anarkali</v>
       </c>
       <c r="C2" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D2">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>S, M, L, XL</v>
+        <v>S, M, L, XL, XXL</v>
       </c>
       <c r="G2" t="str">
-        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
+        <v>c1b7c2ba-7b2a-4217-b1a8-84cba3b5ac10_1792596038728-6201.jpg</v>
       </c>
       <c r="H2" t="str">
-        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
+        <v>c1b7c2ba-7b2a-4217-b1a8-84cba3b5ac10_1792596038728-6201.jpg</v>
       </c>
       <c r="I2" t="str">
-        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
+        <v>c1b7c2ba-7b2a-4217-b1a8-84cba3b5ac10_1792596038728-6201.jpg</v>
       </c>
       <c r="J2" t="str">
         <v>In Stock</v>
       </c>
       <c r="K2" t="str">
-        <v>Fresh Arrivals</v>
+        <v>Handcrafted Couture</v>
       </c>
       <c r="L2" t="str">
-        <v>Exude ethereal grace in this breezy azure kaftan, meticulously crafted from lightweight organza and adorned with delicate metallic stripes. The neckline features intricate hand-embellished detailing, making it a perfect choice for sophisticated daytime soirées or intimate festive gatherings. Note: No Return Policy.</v>
+        <v>Draped in a serene pistachio hue, this graceful anarkali features delicate hand-embroidered floral motifs scattered across a flowing silhouette. Crafted from premium breathable fabric with intricate attention to detail, it is an exquisite choice for intimate festive gatherings and daylight celebrations. Note: No Return Policy. Colour combo possible</v>
       </c>
       <c r="M2" t="str">
         <v>Yes</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" xml:space="preserve">
       <c r="A3" t="str">
-        <v>P221</v>
+        <v>P229</v>
       </c>
       <c r="B3" t="str">
-        <v>Classic Plaid Collared</v>
+        <v>Royal Blue Checkered Brocade Lehenga</v>
       </c>
       <c r="C3" t="str">
-        <v>Ladies Wear</v>
+        <v>Customization</v>
       </c>
       <c r="D3">
-        <v>5000</v>
+        <v>6500</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>S, M, L, XL</v>
+        <v>Custom Fit</v>
       </c>
       <c r="G3" t="str">
-        <v>8f5a4626-3db0-4e69-a246-419e546a855b_1789557487096-4376.jpg</v>
+        <v>0dd71144-4cbe-420e-a8ee-f71eaa67e373_1792595947442-9413.jpg</v>
       </c>
       <c r="H3" t="str">
-        <v>716e7a91-0f8a-49de-8690-24045d24f11c_1789557513967-1019.jpg</v>
+        <v>0dd71144-4cbe-420e-a8ee-f71eaa67e373_1792595947442-9413.jpg</v>
       </c>
       <c r="I3" t="str">
-        <v>8f5a4626-3db0-4e69-a246-419e546a855b_1789557487096-4376.jpg</v>
+        <v>0dd71144-4cbe-420e-a8ee-f71eaa67e373_1792595947442-9413.jpg</v>
       </c>
       <c r="J3" t="str">
         <v>In Stock</v>
       </c>
       <c r="K3" t="str">
-        <v>Fresh Arrivals</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Exuding understated elegance, this refined midi dress features a timeless plaid pattern tailored in breathable, high-quality cotton. Its sophisticated notch-collar silhouette and graceful flare make it a versatile choice for intimate festive gatherings or elevated daytime events. Note: No Return Policy.</v>
+        <v>Festive Edit</v>
+      </c>
+      <c r="L3" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exude regal elegance in this vibrant royal blue lehenga, meticulously crafted from fine checkered fabric and adorned with an intricate gold zari border. The ensemble is perfectly paired with a sheer, ethereal dupatta, making it an exquisite choice for weddings and grand festive celebrations. Note: No Return Policy.
+Colour customization</v>
       </c>
       <c r="M3" t="str">
         <v>Yes</v>
@@ -524,31 +525,31 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>P220</v>
+        <v>P228</v>
       </c>
       <c r="B4" t="str">
-        <v>Crinkled Silk Tiered Festive Dress</v>
+        <v>Royal Blue Brocade Halter Lehenga</v>
       </c>
       <c r="C4" t="str">
-        <v>Ladies Wear</v>
+        <v>Customization</v>
       </c>
       <c r="D4">
-        <v>4500</v>
+        <v>8500</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4" t="str">
-        <v>S, M, L, XL</v>
+        <v>Custom Fit</v>
       </c>
       <c r="G4" t="str">
-        <v>20_1788722727417-5687.jpeg</v>
+        <v>679ab098-78ee-4998-a502-7364ac722ed3_1792595910420-8139.jpg</v>
       </c>
       <c r="H4" t="str">
-        <v>20_1788722727417-5687.jpeg</v>
+        <v>679ab098-78ee-4998-a502-7364ac722ed3_1792595910420-8139.jpg</v>
       </c>
       <c r="I4" t="str">
-        <v>20_1788722727417-5687.jpeg</v>
+        <v>679ab098-78ee-4998-a502-7364ac722ed3_1792595910420-8139.jpg</v>
       </c>
       <c r="J4" t="str">
         <v>In Stock</v>
@@ -557,39 +558,39 @@
         <v>Festive Edit</v>
       </c>
       <c r="L4" t="str">
-        <v>This exquisite fusion dress features alternating tiers of olive green and vibrant fuchsia in a beautifully crinkled silk fabric that drapes effortlessly. Accentuated with a delicate gold zari border at the waist and hem, this sleeveless silhouette seamlessly blends traditional elegance with contemporary style, making it perfect for festive gatherings and intimate celebrations. Note: No Return Policy.</v>
+        <v>Exude timeless elegance in this stunning ensemble featuring a rich, navy blue floral brocade halter blouse paired with a fluid, gold-striped ivory lehenga skirt. Meticulously crafted for the modern woman, this silhouette perfectly balances traditional charm with contemporary sophistication, making it an ideal choice for festive celebrations and intimate wedding soirées. Note: No Return Policy.</v>
       </c>
       <c r="M4" t="str">
         <v>Yes</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
-        <v>P219</v>
+        <v>P227</v>
       </c>
       <c r="B5" t="str">
-        <v>Blush Pink Floral Embroidered Dress</v>
+        <v>Draped lehenga set with hand worked corset blouse</v>
       </c>
       <c r="C5" t="str">
-        <v>Ladies Wear</v>
+        <v>Customization</v>
       </c>
       <c r="D5">
-        <v>3500</v>
+        <v>15000</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5" t="str">
-        <v>S, M, L, XL</v>
+        <v>Custom Fit</v>
       </c>
       <c r="G5" t="str">
-        <v>19_1788722006967-4942.jpeg</v>
+        <v>df78600d-20fa-4580-8bad-ed59fc6159e0_1792595672732-9730.jpg</v>
       </c>
       <c r="H5" t="str">
-        <v>19_1788722006967-4942.jpeg</v>
+        <v>df78600d-20fa-4580-8bad-ed59fc6159e0_1792595672732-9730.jpg</v>
       </c>
       <c r="I5" t="str">
-        <v>19_1788722006967-4942.jpeg</v>
+        <v>df78600d-20fa-4580-8bad-ed59fc6159e0_1792595672732-9730.jpg</v>
       </c>
       <c r="J5" t="str">
         <v>In Stock</v>
@@ -597,49 +598,51 @@
       <c r="K5" t="str">
         <v>Fresh Arrivals</v>
       </c>
-      <c r="L5" t="str">
-        <v>Crafted from lightweight, flowing georgette in a dreamy blush pink hue, this ankle-length dress features a flattering square neckline and elegant three-quarter puff sleeves. Delicate hand-embroidered floral borders adorn the bodice, complemented by matching floral motifs along the ruffled hemline for a touch of whimsical charm. Perfect for intimate festive gatherings, daytime celebrations, or elegant soirées, this piece effortlessly blends modern grace with traditional craftsmanship. Note: No Return Policy.</v>
+      <c r="L5" t="str" xml:space="preserve">
+        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
+Note: No Return Policy.</v>
       </c>
       <c r="M5" t="str">
         <v>Yes</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
-        <v>P218</v>
+        <v>P226</v>
       </c>
       <c r="B6" t="str">
-        <v>Midnight Blue Woven Zari Lehenga</v>
+        <v>Co CORD set</v>
       </c>
       <c r="C6" t="str">
-        <v>Ladies Wear</v>
+        <v>Customization</v>
       </c>
       <c r="D6">
-        <v>4500</v>
+        <v>14500</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6" t="str">
-        <v>S, M, L, XL</v>
+        <v>Custom Fit</v>
       </c>
       <c r="G6" t="str">
-        <v>18_1788721975689-8954.jpeg</v>
+        <v>ee81a7c3-99fa-4ec8-ad68-914bfe8e23eb_1792595447908-7401.jpg</v>
       </c>
       <c r="H6" t="str">
-        <v>18_1788721975689-8954.jpeg</v>
+        <v>ee81a7c3-99fa-4ec8-ad68-914bfe8e23eb_1792595447908-7401.jpg</v>
       </c>
       <c r="I6" t="str">
-        <v>18_1788721975689-8954.jpeg</v>
+        <v>ee81a7c3-99fa-4ec8-ad68-914bfe8e23eb_1792595447908-7401.jpg</v>
       </c>
       <c r="J6" t="str">
         <v>In Stock</v>
       </c>
       <c r="K6" t="str">
-        <v>Handcrafted Couture</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Draped in a majestic midnight blue hue, this voluminous flared lehenga features subtle checkered weave accents paired with a rich metallic gold zari woven border at the hemline. Complemented by a tailored elbow-sleeve blouse and a lightweight sheer tulle dupatta trimmed with ornate brocade borders, it stands as a quintessential choice for grand receptions and festive soirées. Note: No Return Policy.</v>
+        <v>Fresh Arrivals</v>
+      </c>
+      <c r="L6" t="str" xml:space="preserve">
+        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
+Note: No Return Policy.</v>
       </c>
       <c r="M6" t="str">
         <v>Yes</v>
@@ -647,31 +650,31 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>P217</v>
+        <v>P225</v>
       </c>
       <c r="B7" t="str">
-        <v>Emerald Ivory Tissue Lehenga Set</v>
+        <v>Midnight Black Elephant Motif Shirt</v>
       </c>
       <c r="C7" t="str">
-        <v>Ladies Wear</v>
+        <v>Mens Wear</v>
       </c>
       <c r="D7">
-        <v>8500</v>
+        <v>5500</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7" t="str">
-        <v>S, M, L, XL</v>
+        <v>Custom Fit</v>
       </c>
       <c r="G7" t="str">
-        <v>16_1788721959182-4092.jpeg</v>
+        <v>931f8cde-b672-4f4e-9c6b-2e2daeb3235a_1792595365641-2250.jpg</v>
       </c>
       <c r="H7" t="str">
-        <v>16_1788721959182-4092.jpeg</v>
+        <v>931f8cde-b672-4f4e-9c6b-2e2daeb3235a_1792595365641-2250.jpg</v>
       </c>
       <c r="I7" t="str">
-        <v>16_1788721959182-4092.jpeg</v>
+        <v>931f8cde-b672-4f4e-9c6b-2e2daeb3235a_1792595365641-2250.jpg</v>
       </c>
       <c r="J7" t="str">
         <v>In Stock</v>
@@ -680,7 +683,7 @@
         <v>Festive Edit</v>
       </c>
       <c r="L7" t="str">
-        <v>Exuding timeless grace, this ensemble features a delicately woven off-white tissue skirt seamlessly paired with a rich emerald green blouse adorned with intricate gold motifs. The look is complete with a lightweight sheer dupatta trimmed in a regal zari lace border, perfect for intimate wedding ceremonies and festive celebrations. Note: No Return Policy.</v>
+        <v>Exude contemporary elegance with this bespoke black shirt, meticulously tailored to feature a striking, intricate gold-thread elephant motif. Perfectly paired with a traditional crisp white mundu, this ensemble bridges the gap between heritage charm and modern sophistication for any festive celebration. Note: No Return Policy.</v>
       </c>
       <c r="M7" t="str">
         <v>Yes</v>
@@ -688,16 +691,16 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>P216</v>
+        <v>P224</v>
       </c>
       <c r="B8" t="str">
-        <v>Teal Zari Kurta and Ivory Skirt</v>
+        <v>Royal Blue Pearl-Embellished Sharara Set</v>
       </c>
       <c r="C8" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D8">
-        <v>6500</v>
+        <v>8500</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -706,13 +709,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G8" t="str">
-        <v>15_1788721934285-9936.jpeg</v>
+        <v>adf15360-3799-4b34-af27-35d50af381f8_1792595274423-3799.jpg</v>
       </c>
       <c r="H8" t="str">
-        <v>15_1788721934285-9936.jpeg</v>
+        <v>adf15360-3799-4b34-af27-35d50af381f8_1792595274423-3799.jpg</v>
       </c>
       <c r="I8" t="str">
-        <v>15_1788721934285-9936.jpeg</v>
+        <v>adf15360-3799-4b34-af27-35d50af381f8_1792595274423-3799.jpg</v>
       </c>
       <c r="J8" t="str">
         <v>In Stock</v>
@@ -721,7 +724,7 @@
         <v>Festive Edit</v>
       </c>
       <c r="L8" t="str">
-        <v>This elegant ensemble features a sleeveless short kurta in deep peacock teal, adorned with delicate gold zari butis and finished with a rich crimson border, paired beautifully with a voluminous off-white flared skirt. Perfect for festive celebrations and intimate wedding gatherings, this contemporary take on traditional Kerala aesthetics exudes effortless grace and sophistication. Note: No Return Policy.</v>
+        <v>Exude timeless elegance in this vibrant royal blue ensemble, meticulously crafted from premium flowy fabric and adorned with delicate pearl-bead detailing along the scalloped hem and neckline. This sophisticated silhouette offers a graceful drape, making it an impeccable choice for intimate wedding festivities or celebratory evening soirées. Note: No Return Policy.</v>
       </c>
       <c r="M8" t="str">
         <v>Yes</v>
@@ -729,81 +732,84 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>P215</v>
+        <v>P223</v>
       </c>
       <c r="B9" t="str">
-        <v>Royal Teal Flared Georgette Anarkali</v>
+        <v>Ivory Kasavu Embroidered Co-ord Set</v>
       </c>
       <c r="C9" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D9">
-        <v>3500</v>
+        <v>6500</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="F9" t="str">
         <v>S, M, L, XL</v>
       </c>
       <c r="G9" t="str">
-        <v>14_1788721913987-3936.jpeg</v>
+        <v>6397eace-b1a3-4af0-b590-f443e7024963_1792595219543-2495.jpg</v>
       </c>
       <c r="H9" t="str">
-        <v>14_1788721913987-3936.jpeg</v>
+        <v>6397eace-b1a3-4af0-b590-f443e7024963_1792595219543-2495.jpg</v>
       </c>
       <c r="I9" t="str">
-        <v>14_1788721913987-3936.jpeg</v>
+        <v>6397eace-b1a3-4af0-b590-f443e7024963_1792595219543-2495.jpg</v>
       </c>
       <c r="J9" t="str">
         <v>In Stock</v>
       </c>
       <c r="K9" t="str">
-        <v>Festive Edit</v>
+        <v>Handcrafted Couture</v>
       </c>
       <c r="L9" t="str">
-        <v>Draped in rich peacock teal georgette, this floor-length Anarkali ensemble exudes timeless elegance with its sweeping flared silhouette and fitted full sleeves. The look is beautifully complemented by a lightweight sheer dupatta adorned with delicate embroidered silver lace borders, making it an exquisite choice for regal celebrations and evening festivities. Note: No Return Policy.</v>
+        <v>Exuding timeless elegance, this ivory ensemble reimagines the traditional Kerala kasavu with a contemporary silhouette and delicate floral embroidery. Perfectly tailored for intimate festive gatherings or sophisticated daytime events, it captures the essence of minimalist luxury. Note: No Return Policy.</v>
       </c>
       <c r="M9" t="str">
         <v>Yes</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" xml:space="preserve">
       <c r="A10" t="str">
-        <v>P214</v>
+        <v>P222</v>
       </c>
       <c r="B10" t="str">
-        <v>Royal Blue Pearl Embellished Sharara Set</v>
+        <v>Azure Striped Organza Kaftan Set</v>
       </c>
       <c r="C10" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D10">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="str">
-        <v>S, M, L, XL</v>
+        <v>Custom Fit</v>
       </c>
       <c r="G10" t="str">
-        <v>13_1788721896896-5264.jpeg</v>
+        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
       </c>
       <c r="H10" t="str">
-        <v>13_1788721896896-5264.jpeg</v>
+        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
       </c>
       <c r="I10" t="str">
-        <v>13_1788721896896-5264.jpeg</v>
+        <v>286f3771-f4d7-4ab8-8381-16d200e651d6_1789557548681-4742.jpg</v>
       </c>
       <c r="J10" t="str">
         <v>In Stock</v>
       </c>
       <c r="K10" t="str">
-        <v>Festive Edit</v>
-      </c>
-      <c r="L10" t="str">
-        <v>Rendered in an opulent royal blue georgette fabric, this breathtaking ensemble features a short tunic delicately detailed with pearl work along the square neckline and scalloped hemline. Paired with a gracefully voluminous flared bottom and a translucent dupatta bordered in pearls, it creates a silhouette of captivating elegance. Ideal for festive soirees, sangeet celebrations, and grand evening receptions. Note: No Return Policy.</v>
+        <v>Fresh Arrivals</v>
+      </c>
+      <c r="L10" t="str" xml:space="preserve">
+        <v xml:space="preserve">Exude ethereal grace in this breezy azure kaftan, meticulously crafted from lightweight organza and adorned with delicate metallic stripes. The neckline features intricate hand-embellished detailing, making it a perfect choice for sophisticated daytime soirées or intimate festive gatherings. 
+Note: No Return Policy.
+No COD
+Please check the size chart</v>
       </c>
       <c r="M10" t="str">
         <v>Yes</v>
@@ -811,16 +817,16 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>P213</v>
+        <v>P221</v>
       </c>
       <c r="B11" t="str">
-        <v>Teal Wave Print Jacket Ensemble</v>
+        <v>Classic Plaid Collared</v>
       </c>
       <c r="C11" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D11">
-        <v>4500</v>
+        <v>5000</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -829,13 +835,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G11" t="str">
-        <v>12_1788721878497-6401.jpeg</v>
+        <v>8f5a4626-3db0-4e69-a246-419e546a855b_1789557487096-4376.jpg</v>
       </c>
       <c r="H11" t="str">
-        <v>12_1788721878497-6401.jpeg</v>
+        <v>716e7a91-0f8a-49de-8690-24045d24f11c_1789557513967-1019.jpg</v>
       </c>
       <c r="I11" t="str">
-        <v>12_1788721878497-6401.jpeg</v>
+        <v>8f5a4626-3db0-4e69-a246-419e546a855b_1789557487096-4376.jpg</v>
       </c>
       <c r="J11" t="str">
         <v>In Stock</v>
@@ -844,7 +850,7 @@
         <v>Fresh Arrivals</v>
       </c>
       <c r="L11" t="str">
-        <v>Exquisitely tailored in vibrant ocean-teal tones, this modern two-piece ensemble features a sleek inner dress layered under a mandarin-collared jacket adorned with rhythmic chevron wave patterns. Designed with seamless side pockets and effortless drape, it is an ideal choice for boutique gatherings, festive lunches, and contemporary soirées. Note: No Return Policy.</v>
+        <v>Exuding understated elegance, this refined midi dress features a timeless plaid pattern tailored in breathable, high-quality cotton. Its sophisticated notch-collar silhouette and graceful flare make it a versatile choice for intimate festive gatherings or elevated daytime events. Note: No Return Policy.</v>
       </c>
       <c r="M11" t="str">
         <v>Yes</v>
@@ -852,16 +858,16 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>P212</v>
+        <v>P220</v>
       </c>
       <c r="B12" t="str">
-        <v>Midnight Blue Shimmer Anarkali Gown</v>
+        <v>Crinkled Silk Tiered Festive Dress</v>
       </c>
       <c r="C12" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D12">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -870,13 +876,13 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G12" t="str">
-        <v>11_1788721855287-4057.jpeg</v>
+        <v>20_1788722727417-5687.jpeg</v>
       </c>
       <c r="H12" t="str">
-        <v>11_1788721855287-4057.jpeg</v>
+        <v>20_1788722727417-5687.jpeg</v>
       </c>
       <c r="I12" t="str">
-        <v>11_1788721855287-4057.jpeg</v>
+        <v>20_1788722727417-5687.jpeg</v>
       </c>
       <c r="J12" t="str">
         <v>In Stock</v>
@@ -885,7 +891,7 @@
         <v>Festive Edit</v>
       </c>
       <c r="L12" t="str">
-        <v>Crafted in deep navy georgette woven with luminous metallic zari pinstripes, this sleeveless Anarkali gown embodies effortless modern grace. The structured V-neckline is highlighted with delicate hand-stitched detailing, cascading gracefully into a voluminous, fluid silhouette ideal for evening celebrations and festive gatherings. Note: No Return Policy.</v>
+        <v>This exquisite fusion dress features alternating tiers of olive green and vibrant fuchsia in a beautifully crinkled silk fabric that drapes effortlessly. Accentuated with a delicate gold zari border at the waist and hem, this sleeveless silhouette seamlessly blends traditional elegance with contemporary style, making it perfect for festive gatherings and intimate celebrations. Note: No Return Policy.</v>
       </c>
       <c r="M12" t="str">
         <v>Yes</v>
@@ -893,16 +899,16 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>P211</v>
+        <v>P219</v>
       </c>
       <c r="B13" t="str">
-        <v>Crimson Gold Embellished Bridal Lehenga</v>
+        <v>Blush Pink Floral Embroidered Dress</v>
       </c>
       <c r="C13" t="str">
         <v>Ladies Wear</v>
       </c>
       <c r="D13">
-        <v>25000</v>
+        <v>3500</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -911,22 +917,22 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G13" t="str">
-        <v>10_1788721631854-5301.png</v>
+        <v>19_1788722006967-4942.jpeg</v>
       </c>
       <c r="H13" t="str">
-        <v>10_1788721631854-5301.png</v>
+        <v>19_1788722006967-4942.jpeg</v>
       </c>
       <c r="I13" t="str">
-        <v>10_1788721631854-5301.png</v>
+        <v>19_1788722006967-4942.jpeg</v>
       </c>
       <c r="J13" t="str">
         <v>In Stock</v>
       </c>
       <c r="K13" t="str">
-        <v>Bridal Heritage</v>
+        <v>Fresh Arrivals</v>
       </c>
       <c r="L13" t="str">
-        <v>Exuding regal splendor, this opulent bridal ensemble features a richly detailed crimson blouse adorned with intricate zardozi hand embroidery and sheer embellished sleeves, paired with a shimmering woven gold lehenga skirt. Completed with a luxurious tissue dupatta, it is meticulously tailored for grand wedding receptions and evening celebrations. Note: No Return Policy.</v>
+        <v>Crafted from lightweight, flowing georgette in a dreamy blush pink hue, this ankle-length dress features a flattering square neckline and elegant three-quarter puff sleeves. Delicate hand-embroidered floral borders adorn the bodice, complemented by matching floral motifs along the ruffled hemline for a touch of whimsical charm. Perfect for intimate festive gatherings, daytime celebrations, or elegant soirées, this piece effortlessly blends modern grace with traditional craftsmanship. Note: No Return Policy.</v>
       </c>
       <c r="M13" t="str">
         <v>Yes</v>
@@ -934,10 +940,10 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>P210</v>
+        <v>P218</v>
       </c>
       <c r="B14" t="str">
-        <v>Royal Blue Brocade Halter Blouse</v>
+        <v>Midnight Blue Woven Zari Lehenga</v>
       </c>
       <c r="C14" t="str">
         <v>Ladies Wear</v>
@@ -952,54 +958,54 @@
         <v>S, M, L, XL</v>
       </c>
       <c r="G14" t="str">
-        <v>9_1788721582211-8463.png</v>
+        <v>18_1788721975689-8954.jpeg</v>
       </c>
       <c r="H14" t="str">
-        <v>9_1788721582211-8463.png</v>
+        <v>18_1788721975689-8954.jpeg</v>
       </c>
       <c r="I14" t="str">
-        <v>9_1788721582211-8463.png</v>
+        <v>18_1788721975689-8954.jpeg</v>
       </c>
       <c r="J14" t="str">
         <v>In Stock</v>
       </c>
       <c r="K14" t="str">
-        <v>Festive Edit</v>
+        <v>Handcrafted Couture</v>
       </c>
       <c r="L14" t="str">
-        <v>Impeccably tailored from lustrous royal blue silk brocade, this high-neck halter blouse features intricate woven gold zari floral motifs that radiate contemporary charm. Perfectly paired with ivory kasavu drapes or festive lehengas, it offers a striking silhouette ideal for evening celebrations and wedding receptions. Note: No Return Policy.</v>
+        <v>Draped in a majestic midnight blue hue, this voluminous flared lehenga features subtle checkered weave accents paired with a rich metallic gold zari woven border at the hemline. Complemented by a tailored elbow-sleeve blouse and a lightweight sheer tulle dupatta trimmed with ornate brocade borders, it stands as a quintessential choice for grand receptions and festive soirées. Note: No Return Policy.</v>
       </c>
       <c r="M14" t="str">
         <v>Yes</v>
       </c>
     </row>
-    <row r="15" xml:space="preserve">
+    <row r="15">
       <c r="A15" t="str">
-        <v>P209</v>
+        <v>P217</v>
       </c>
       <c r="B15" t="str">
-        <v>Ivory Kasavu Striped Kurta Mundu Set</v>
+        <v>Emerald Ivory Tissue Lehenga Set</v>
       </c>
       <c r="C15" t="str">
-        <v>Mens Wear</v>
+        <v>Ladies Wear</v>
       </c>
       <c r="D15">
-        <v>3500</v>
+        <v>8500</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15" t="str">
-        <v>38 (S), 40 (M), 42 (L), 44 (XL)</v>
+        <v>S, M, L, XL</v>
       </c>
       <c r="G15" t="str">
-        <v>8_1788721559495-2695.png</v>
+        <v>16_1788721959182-4092.jpeg</v>
       </c>
       <c r="H15" t="str">
-        <v>8_1788721559495-2695.png</v>
+        <v>16_1788721959182-4092.jpeg</v>
       </c>
       <c r="I15" t="str">
-        <v>8_1788721559495-2695.png</v>
+        <v>16_1788721959182-4092.jpeg</v>
       </c>
       <c r="J15" t="str">
         <v>In Stock</v>
@@ -1007,314 +1013,560 @@
       <c r="K15" t="str">
         <v>Festive Edit</v>
       </c>
-      <c r="L15" t="str" xml:space="preserve">
+      <c r="L15" t="str">
+        <v>Exuding timeless grace, this ensemble features a delicately woven off-white tissue skirt seamlessly paired with a rich emerald green blouse adorned with intricate gold motifs. The look is complete with a lightweight sheer dupatta trimmed in a regal zari lace border, perfect for intimate wedding ceremonies and festive celebrations. Note: No Return Policy.</v>
+      </c>
+      <c r="M15" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>P216</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Teal Zari Kurta and Ivory Skirt</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D16">
+        <v>6500</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G16" t="str">
+        <v>15_1788721934285-9936.jpeg</v>
+      </c>
+      <c r="H16" t="str">
+        <v>15_1788721934285-9936.jpeg</v>
+      </c>
+      <c r="I16" t="str">
+        <v>15_1788721934285-9936.jpeg</v>
+      </c>
+      <c r="J16" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K16" t="str">
+        <v>Festive Edit</v>
+      </c>
+      <c r="L16" t="str">
+        <v>This elegant ensemble features a sleeveless short kurta in deep peacock teal, adorned with delicate gold zari butis and finished with a rich crimson border, paired beautifully with a voluminous off-white flared skirt. Perfect for festive celebrations and intimate wedding gatherings, this contemporary take on traditional Kerala aesthetics exudes effortless grace and sophistication. Note: No Return Policy.</v>
+      </c>
+      <c r="M16" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>P215</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Royal Teal Flared Georgette Anarkali</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D17">
+        <v>3500</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G17" t="str">
+        <v>14_1788721913987-3936.jpeg</v>
+      </c>
+      <c r="H17" t="str">
+        <v>14_1788721913987-3936.jpeg</v>
+      </c>
+      <c r="I17" t="str">
+        <v>14_1788721913987-3936.jpeg</v>
+      </c>
+      <c r="J17" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K17" t="str">
+        <v>Festive Edit</v>
+      </c>
+      <c r="L17" t="str">
+        <v>Draped in rich peacock teal georgette, this floor-length Anarkali ensemble exudes timeless elegance with its sweeping flared silhouette and fitted full sleeves. The look is beautifully complemented by a lightweight sheer dupatta adorned with delicate embroidered silver lace borders, making it an exquisite choice for regal celebrations and evening festivities. Note: No Return Policy.</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>P213</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Teal Wave Print Jacket Ensemble</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D18">
+        <v>4500</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+      <c r="F18" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G18" t="str">
+        <v>12_1788721878497-6401.jpeg</v>
+      </c>
+      <c r="H18" t="str">
+        <v>12_1788721878497-6401.jpeg</v>
+      </c>
+      <c r="I18" t="str">
+        <v>12_1788721878497-6401.jpeg</v>
+      </c>
+      <c r="J18" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K18" t="str">
+        <v>Fresh Arrivals</v>
+      </c>
+      <c r="L18" t="str">
+        <v>Exquisitely tailored in vibrant ocean-teal tones, this modern two-piece ensemble features a sleek inner dress layered under a mandarin-collared jacket adorned with rhythmic chevron wave patterns. Designed with seamless side pockets and effortless drape, it is an ideal choice for boutique gatherings, festive lunches, and contemporary soirées. Note: No Return Policy.</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>P212</v>
+      </c>
+      <c r="B19" t="str">
+        <v>Midnight Blue Shimmer Anarkali Gown</v>
+      </c>
+      <c r="C19" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D19">
+        <v>3750</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G19" t="str">
+        <v>11_1788721855287-4057.jpeg</v>
+      </c>
+      <c r="H19" t="str">
+        <v>11_1788721855287-4057.jpeg</v>
+      </c>
+      <c r="I19" t="str">
+        <v>11_1788721855287-4057.jpeg</v>
+      </c>
+      <c r="J19" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K19" t="str">
+        <v>Festive Edit</v>
+      </c>
+      <c r="L19" t="str">
+        <v>Crafted in deep navy georgette woven with luminous metallic zari pinstripes, this sleeveless Anarkali gown embodies effortless modern grace. The structured V-neckline is highlighted with delicate hand-stitched detailing, cascading gracefully into a voluminous, fluid silhouette ideal for evening celebrations and festive gatherings. Note: No Return Policy.</v>
+      </c>
+      <c r="M19" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>P211</v>
+      </c>
+      <c r="B20" t="str">
+        <v>Crimson Gold Embellished Bridal Lehenga</v>
+      </c>
+      <c r="C20" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="D20">
+        <v>35000</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="str">
+        <v>Custom Fit</v>
+      </c>
+      <c r="G20" t="str">
+        <v>10_1788721631854-5301.png</v>
+      </c>
+      <c r="H20" t="str">
+        <v>10_1788721631854-5301.png</v>
+      </c>
+      <c r="I20" t="str">
+        <v>10_1788721631854-5301.png</v>
+      </c>
+      <c r="J20" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K20" t="str">
+        <v>Bridal Heritage</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Exuding regal splendor, this opulent bridal ensemble features a richly detailed crimson blouse adorned with intricate zardozi hand embroidery and sheer embellished sleeves, paired with a shimmering woven gold lehenga skirt. Completed with a luxurious tissue dupatta, it is meticulously tailored for grand wedding receptions and evening celebrations. Note: No Return Policy.</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>P210</v>
+      </c>
+      <c r="B21" t="str">
+        <v>Royal Blue Brocade Halter Blouse</v>
+      </c>
+      <c r="C21" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D21">
+        <v>4500</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G21" t="str">
+        <v>9_1788721582211-8463.png</v>
+      </c>
+      <c r="H21" t="str">
+        <v>9_1788721582211-8463.png</v>
+      </c>
+      <c r="I21" t="str">
+        <v>9_1788721582211-8463.png</v>
+      </c>
+      <c r="J21" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K21" t="str">
+        <v>Festive Edit</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Impeccably tailored from lustrous royal blue silk brocade, this high-neck halter blouse features intricate woven gold zari floral motifs that radiate contemporary charm. Perfectly paired with ivory kasavu drapes or festive lehengas, it offers a striking silhouette ideal for evening celebrations and wedding receptions. Note: No Return Policy.</v>
+      </c>
+      <c r="M21" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="22" xml:space="preserve">
+      <c r="A22" t="str">
+        <v>P209</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Ivory Kasavu Striped Kurta Mundu Set</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Mens Wear</v>
+      </c>
+      <c r="D22">
+        <v>3500</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+      <c r="F22" t="str">
+        <v>38 (S), 40 (M), 42 (L), 44 (XL)</v>
+      </c>
+      <c r="G22" t="str">
+        <v>8_1788721559495-2695.png</v>
+      </c>
+      <c r="H22" t="str">
+        <v>8_1788721559495-2695.png</v>
+      </c>
+      <c r="I22" t="str">
+        <v>8_1788721559495-2695.png</v>
+      </c>
+      <c r="J22" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K22" t="str">
+        <v>Festive Edit</v>
+      </c>
+      <c r="L22" t="str" xml:space="preserve">
         <v xml:space="preserve">Imbued with understated elegance, this pristine off-white kurta features delicate vertical gold kasavu zari stripes for a refined festive charm. Paired impeccably with a traditional golden zari-bordered mundu, this ensemble honors Kerala's rich sartorial heritage with contemporary elegance. Perfect for Onam celebrations, traditional wedding ceremonies, and auspicious festive rituals.
 Note: No Return Policy.</v>
       </c>
-      <c r="M15" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="16" xml:space="preserve">
-      <c r="A16" t="str">
-        <v>P208</v>
-      </c>
-      <c r="B16" t="str">
-        <v>Ivory Floral Hand-Painted Kasavu Saree</v>
-      </c>
-      <c r="C16" t="str">
-        <v>Ladies Wear</v>
-      </c>
-      <c r="D16">
-        <v>5000</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-      <c r="F16" t="str">
-        <v>S, M, L, XL</v>
-      </c>
-      <c r="G16" t="str">
-        <v>7_1788721516950-7398.png</v>
-      </c>
-      <c r="H16" t="str">
-        <v>7_1788721516950-7398.png</v>
-      </c>
-      <c r="I16" t="str">
-        <v>7_1788721516950-7398.png</v>
-      </c>
-      <c r="J16" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K16" t="str">
-        <v>Handcrafted Couture</v>
-      </c>
-      <c r="L16" t="str" xml:space="preserve">
-        <v xml:space="preserve">This exquisite ivory Kasavu saree celebrates Kerala's rich heritage, beautifully adorned with delicate, hand-painted floral motifs in soft pink and leafy green hues. Crafted from premium handloom cotton, it features a classic golden zari border paired with a matching puff-sleeved blouse that exudes vintage grace. Perfect for Onam festivities, temple visits, or intimate wedding celebrations, this drape is a timeless ode to traditional elegance.
-Note: No Return Policy.</v>
-      </c>
-      <c r="M16" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="17" xml:space="preserve">
-      <c r="A17" t="str">
+      <c r="M22" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="23" xml:space="preserve">
+      <c r="A23" t="str">
         <v>P207</v>
       </c>
-      <c r="B17" t="str">
+      <c r="B23" t="str">
         <v>Ivory Kasavu Embroidered Corset Gown</v>
       </c>
-      <c r="C17" t="str">
+      <c r="C23" t="str">
         <v>Customization</v>
       </c>
-      <c r="D17">
+      <c r="D23">
         <v>14000</v>
       </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-      <c r="F17" t="str">
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="str">
         <v>Custom Fit</v>
       </c>
-      <c r="G17" t="str">
+      <c r="G23" t="str">
         <v>5_1788721479116-3197.png</v>
       </c>
-      <c r="H17" t="str">
+      <c r="H23" t="str">
         <v>5_1788721479116-3197.png</v>
       </c>
-      <c r="I17" t="str">
+      <c r="I23" t="str">
         <v>5_1788721479116-3197.png</v>
       </c>
-      <c r="J17" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K17" t="str">
+      <c r="J23" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K23" t="str">
         <v>Bespoke Couture</v>
       </c>
-      <c r="L17" t="str" xml:space="preserve">
+      <c r="L23" t="str" xml:space="preserve">
         <v xml:space="preserve">Reimagining traditional Kerala heritage with modern allure, this ivory gown features a structured strapless corset bodice delicately detailed with hand-embroidered golden motifs. Highlighted by classic golden Kasavu zari borders running down the fitted silhouette, it effortlessly blends regal grace with contemporary elegance. Perfectly suited for grand wedding receptions, engagement ceremonies, and opulent festive celebrations.
 Note: No Return Policy.</v>
       </c>
-      <c r="M17" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="18" xml:space="preserve">
-      <c r="A18" t="str">
+      <c r="M23" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="24" xml:space="preserve">
+      <c r="A24" t="str">
         <v>P206</v>
       </c>
-      <c r="B18" t="str">
+      <c r="B24" t="str">
         <v>Scarlet Embroidered Organza Fusion Set</v>
       </c>
-      <c r="C18" t="str">
-        <v>Ladies Wear</v>
-      </c>
-      <c r="D18">
-        <v>3550</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-      <c r="F18" t="str">
-        <v>S, M, L, XL</v>
-      </c>
-      <c r="G18" t="str">
+      <c r="C24" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="D24">
+        <v>5500</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24" t="str">
+        <v>Custom Fit</v>
+      </c>
+      <c r="G24" t="str">
         <v>6_1788721385434-2405.png</v>
       </c>
-      <c r="H18" t="str">
+      <c r="H24" t="str">
         <v>6_1788721385434-2405.png</v>
       </c>
-      <c r="I18" t="str">
+      <c r="I24" t="str">
         <v>6_1788721385434-2405.png</v>
       </c>
-      <c r="J18" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K18" t="str">
+      <c r="J24" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K24" t="str">
         <v>Festive Edit</v>
       </c>
-      <c r="L18" t="str" xml:space="preserve">
+      <c r="L24" t="str" xml:space="preserve">
         <v xml:space="preserve">Radiate contemporary elegance in this striking scarlet red fusion ensemble, featuring a tailored bustier paired with fluid trousers and a sheer organza longline jacket. The lightweight jacket is beautifully elevated by delicate scalloped gold zari embroidery tracing the borders and cuffs, adding a touch of traditional craftsmanship to a modern silhouette. Perfect for festive soirées, pre-wedding celebrations, or evening receptions, this ensemble effortlessly balances modern sophistication with timeless grace.
 Note: No Return Policy.</v>
       </c>
-      <c r="M18" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="19" xml:space="preserve">
-      <c r="A19" t="str">
+      <c r="M24" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="25" xml:space="preserve">
+      <c r="A25" t="str">
         <v>P201</v>
       </c>
-      <c r="B19" t="str">
+      <c r="B25" t="str">
         <v>Hand painted Kerala Kasavu saree</v>
       </c>
-      <c r="C19" t="str">
+      <c r="C25" t="str">
         <v>Ladies Wear</v>
       </c>
-      <c r="D19">
-        <v>4200</v>
-      </c>
-      <c r="E19">
+      <c r="D25">
+        <v>4900</v>
+      </c>
+      <c r="E25">
         <v>4950</v>
       </c>
-      <c r="F19" t="str">
+      <c r="F25" t="str">
         <v>S, M, L, XL</v>
       </c>
-      <c r="G19" t="str">
+      <c r="G25" t="str">
         <v>7_1788628563833-9707.png</v>
       </c>
-      <c r="H19" t="str">
+      <c r="H25" t="str">
         <v>7_1788628563833-9707.png</v>
       </c>
-      <c r="I19" t="str">
+      <c r="I25" t="str">
         <v>7_1788628563833-9707.png</v>
       </c>
-      <c r="J19" t="str">
+      <c r="J25" t="str">
         <v>Made to Order</v>
       </c>
-      <c r="K19" t="str">
+      <c r="K25" t="str">
         <v>Fresh Arrivals</v>
       </c>
-      <c r="L19" t="str" xml:space="preserve">
+      <c r="L25" t="str" xml:space="preserve">
+        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
+Note: No Return Policy.
+Blouse unstitched</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="26" xml:space="preserve">
+      <c r="A26" t="str">
+        <v>P203</v>
+      </c>
+      <c r="B26" t="str">
+        <v>Purple gown</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="D26">
+        <v>17500</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26" t="str">
+        <v>Custom Fit</v>
+      </c>
+      <c r="G26" t="str">
+        <v>3_1788531630686-7753.jpeg</v>
+      </c>
+      <c r="H26" t="str">
+        <v>3_1788531630686-7753.jpeg</v>
+      </c>
+      <c r="I26" t="str">
+        <v>3_1788531630686-7753.jpeg</v>
+      </c>
+      <c r="J26" t="str">
+        <v>Limited Stock</v>
+      </c>
+      <c r="K26" t="str">
+        <v>Fresh Arrivals</v>
+      </c>
+      <c r="L26" t="str" xml:space="preserve">
         <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
 Note: No Return Policy.</v>
       </c>
-      <c r="M19" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="20" xml:space="preserve">
-      <c r="A20" t="str">
-        <v>P203</v>
-      </c>
-      <c r="B20" t="str">
-        <v>Purple gown</v>
-      </c>
-      <c r="C20" t="str">
-        <v>Customization</v>
-      </c>
-      <c r="D20">
-        <v>17500</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" t="str">
-        <v>Custom Fit</v>
-      </c>
-      <c r="G20" t="str">
-        <v>3_1788531630686-7753.jpeg</v>
-      </c>
-      <c r="H20" t="str">
-        <v>3_1788531630686-7753.jpeg</v>
-      </c>
-      <c r="I20" t="str">
-        <v>3_1788531630686-7753.jpeg</v>
-      </c>
-      <c r="J20" t="str">
-        <v>Limited Stock</v>
-      </c>
-      <c r="K20" t="str">
+      <c r="M26" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="27" xml:space="preserve">
+      <c r="A27" t="str">
+        <v>P204</v>
+      </c>
+      <c r="B27" t="str">
+        <v>Ivory top and pant</v>
+      </c>
+      <c r="C27" t="str">
+        <v>Ladies Wear</v>
+      </c>
+      <c r="D27">
+        <v>6500</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27" t="str">
+        <v>S, M, L, XL</v>
+      </c>
+      <c r="G27" t="str">
+        <v>1_1788531606882-8672.jpeg</v>
+      </c>
+      <c r="H27" t="str">
+        <v>1_1788531606882-8672.jpeg</v>
+      </c>
+      <c r="I27" t="str">
+        <v>1_1788531606882-8672.jpeg</v>
+      </c>
+      <c r="J27" t="str">
+        <v>In Stock</v>
+      </c>
+      <c r="K27" t="str">
         <v>Fresh Arrivals</v>
       </c>
-      <c r="L20" t="str" xml:space="preserve">
+      <c r="L27" t="str" xml:space="preserve">
         <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
 Note: No Return Policy.</v>
       </c>
-      <c r="M20" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="21" xml:space="preserve">
-      <c r="A21" t="str">
-        <v>P204</v>
-      </c>
-      <c r="B21" t="str">
-        <v>Ivory top and pant</v>
-      </c>
-      <c r="C21" t="str">
-        <v>Ladies Wear</v>
-      </c>
-      <c r="D21">
-        <v>6500</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" t="str">
-        <v>S, M, L, XL</v>
-      </c>
-      <c r="G21" t="str">
-        <v>1_1788531606882-8672.jpeg</v>
-      </c>
-      <c r="H21" t="str">
-        <v>1_1788531606882-8672.jpeg</v>
-      </c>
-      <c r="I21" t="str">
-        <v>1_1788531606882-8672.jpeg</v>
-      </c>
-      <c r="J21" t="str">
-        <v>In Stock</v>
-      </c>
-      <c r="K21" t="str">
+      <c r="M27" t="str">
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="28" xml:space="preserve">
+      <c r="A28" t="str">
+        <v>P205</v>
+      </c>
+      <c r="B28" t="str">
+        <v>MODAL SLIK KAFTAN</v>
+      </c>
+      <c r="C28" t="str">
+        <v>Customization</v>
+      </c>
+      <c r="D28">
+        <v>9500</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28" t="str">
+        <v>Custom Fit</v>
+      </c>
+      <c r="G28" t="str">
+        <v>2_1788531469161-2419.jpeg</v>
+      </c>
+      <c r="H28" t="str">
+        <v>2_1788531469161-2419.jpeg</v>
+      </c>
+      <c r="I28" t="str">
+        <v>2_1788531469161-2419.jpeg</v>
+      </c>
+      <c r="J28" t="str">
+        <v>Made to Order</v>
+      </c>
+      <c r="K28" t="str">
         <v>Fresh Arrivals</v>
       </c>
-      <c r="L21" t="str" xml:space="preserve">
-        <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
-Note: No Return Policy.</v>
-      </c>
-      <c r="M21" t="str">
-        <v>Yes</v>
-      </c>
-    </row>
-    <row r="22" xml:space="preserve">
-      <c r="A22" t="str">
-        <v>P205</v>
-      </c>
-      <c r="B22" t="str">
-        <v>MODAL SLIK KAFTAN</v>
-      </c>
-      <c r="C22" t="str">
-        <v>Customization</v>
-      </c>
-      <c r="D22">
-        <v>7500</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-      <c r="F22" t="str">
-        <v>Custom Fit</v>
-      </c>
-      <c r="G22" t="str">
-        <v>2_1788531469161-2419.jpeg</v>
-      </c>
-      <c r="H22" t="str">
-        <v>2_1788531469161-2419.jpeg</v>
-      </c>
-      <c r="I22" t="str">
-        <v>2_1788531469161-2419.jpeg</v>
-      </c>
-      <c r="J22" t="str">
-        <v>Made to Order</v>
-      </c>
-      <c r="K22" t="str">
-        <v>Fresh Arrivals</v>
-      </c>
-      <c r="L22" t="str" xml:space="preserve">
+      <c r="L28" t="str" xml:space="preserve">
         <v xml:space="preserve">Handcrafted designer creation by Naomika Design Studio.
 Neck hand worked
 above excel price will vary 500-1000 rs
 customization possible
 Note: No Return Policy.</v>
       </c>
-      <c r="M22" t="str">
+      <c r="M28" t="str">
         <v>Yes</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:M22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M28"/>
   </ignoredErrors>
 </worksheet>
 </file>